--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,374 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D193</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Work-related mental disorder</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>职业相关精神障碍</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>206</v>
       </c>
-      <c r="N2" t="n">
-        <v>5.282051282051282</v>
-      </c>
       <c r="O2" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.09645880685798612</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D193</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>work-related-mental-disorder</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D193</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>职业相关精神障碍</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>206</v>
+      </c>
+      <c r="O3" t="n">
+        <v>206</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_BR_SINAN</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Work-related mental disorder</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:BR:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>SINAN MENT work-related mental disorder notifications.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>final; provisional</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_BR_WORK_MENTAL_MENT</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -779,7 +1201,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -789,52 +1211,94 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>206</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>206</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.09645880685798612</v>
       </c>

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">

--- a/diseases/d193/2026-2029.xlsx
+++ b/diseases/d193/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
